--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -1022,34 +1022,34 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>8748000</v>
+        <v>7960600</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>25805</v>
+        <v>23483</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>7960680</v>
+        <v>7960600</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>23483</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18909,12 +18909,12 @@
 (26年-07月-03日)</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>H | 339呎 (2房)
-$875万
-$25,805/呎
-(在售)</t>
+$796万
+$23,483/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -18914,7 +18914,7 @@
           <t>H | 339呎 (2房)
 $796万
 $23,483/呎
-(26年-09月-06日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="J5" s="23" t="inlineStr">

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -8804,34 +8804,34 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
-        <v>10839000</v>
+        <v>9863400</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>25148</v>
+        <v>22885</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>9863490</v>
+        <v>9863400</v>
       </c>
       <c r="L132" s="5" t="n">
         <v>22885</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19899,12 +19899,12 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 431呎 (2房)
-$1084万
-$25,148/呎
-(在售)</t>
+$986万
+$22,885/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -6564,34 +6564,34 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>10952000</v>
+        <v>9966300</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>25411</v>
+        <v>23124</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>9966320</v>
+        <v>9966300</v>
       </c>
       <c r="L96" s="5" t="n">
         <v>23124</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>247</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -19590,12 +19590,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 431呎 (2房)
-$1095万
-$25,411/呎
-(在售)</t>
+$997万
+$23,124/呎
+(26年-10月-03日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -8809,7 +8809,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -19904,7 +19904,7 @@
           <t>C | 431呎 (2房)
 $986万
 $22,885/呎
-(26年-09月-27日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">

--- a/files/九龙-红磡-首岸第3期.xlsx
+++ b/files/九龙-红磡-首岸第3期.xlsx
@@ -6569,7 +6569,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -19595,7 +19595,7 @@
           <t>C | 431呎 (2房)
 $997万
 $23,124/呎
-(26年-10月-03日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
